--- a/data/parrotfish data/parrotfish_metadata.xlsx
+++ b/data/parrotfish data/parrotfish_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JonathanB22\Desktop\Dan\Eilat_2017_MHW\Red_Sea_MHWs_Parrotfish\data\parrotfish data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{219A8B13-2D57-4C26-AE78-4A3740413C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8E95CA0-4DEA-400E-AB0C-0A3AB45B34B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{FB66EAEE-B1FF-4CD3-9195-8C463EB6069F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{FB66EAEE-B1FF-4CD3-9195-8C463EB6069F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/data/parrotfish data/parrotfish_metadata.xlsx
+++ b/data/parrotfish data/parrotfish_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JonathanB22\Desktop\Dan\Eilat_2017_MHW\Red_Sea_MHWs_Parrotfish\data\parrotfish data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8E95CA0-4DEA-400E-AB0C-0A3AB45B34B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6BDCE18-53A2-4A73-BEF7-E763F7432722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{FB66EAEE-B1FF-4CD3-9195-8C463EB6069F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{FB66EAEE-B1FF-4CD3-9195-8C463EB6069F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="26">
   <si>
     <t>TB</t>
   </si>
@@ -78,9 +78,6 @@
     <t>V13A-1x</t>
   </si>
   <si>
-    <t>C.gibbus</t>
-  </si>
-  <si>
     <t>S. ferrugineus</t>
   </si>
   <si>
@@ -111,13 +108,13 @@
     <t>Length type</t>
   </si>
   <si>
-    <t>Weight (kg)</t>
-  </si>
-  <si>
-    <t>Length (m)</t>
-  </si>
-  <si>
     <t>Frequency (kHz)</t>
+  </si>
+  <si>
+    <t>Length (cm)</t>
+  </si>
+  <si>
+    <t>Weight (gr)</t>
   </si>
 </sst>
 </file>
@@ -125,7 +122,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -186,9 +183,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -196,13 +203,10 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -517,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2DFE37B-8115-4383-BF32-AB20208DA830}">
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
@@ -525,56 +529,55 @@
     <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D2" s="1">
-        <v>19111339</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0.35499999999999998</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0.90300000000000002</v>
-      </c>
+        <v>1212923</v>
+      </c>
+      <c r="E2" s="6">
+        <v>29.7</v>
+      </c>
+      <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
@@ -582,56 +585,56 @@
         <v>3</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1">
-        <v>73</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1">
-        <v>19111342</v>
-      </c>
-      <c r="E3" s="1">
-        <v>0.36499999999999999</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0.81799999999999995</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="5">
+        <v>69</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1273484</v>
+      </c>
+      <c r="E3" s="7">
+        <v>31.8</v>
+      </c>
+      <c r="F3" s="7">
+        <v>465</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B4" s="1">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D4" s="1">
-        <v>19111348</v>
-      </c>
-      <c r="E4" s="1">
-        <v>0.35299999999999998</v>
-      </c>
-      <c r="F4" s="3">
-        <v>0.86</v>
+        <v>1273489</v>
+      </c>
+      <c r="E4" s="6">
+        <v>34.300000000000004</v>
+      </c>
+      <c r="F4" s="6">
+        <v>830</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>2</v>
@@ -640,28 +643,26 @@
         <v>3</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B5" s="1">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D5" s="1">
-        <v>19111351</v>
-      </c>
-      <c r="E5" s="1">
-        <v>0.35299999999999998</v>
-      </c>
-      <c r="F5" s="3">
-        <v>0.85</v>
-      </c>
+        <v>1212924</v>
+      </c>
+      <c r="E5" s="6">
+        <v>28.499999999999996</v>
+      </c>
+      <c r="F5" s="6"/>
       <c r="G5" s="1" t="s">
         <v>2</v>
       </c>
@@ -669,27 +670,27 @@
         <v>3</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D6" s="1">
-        <v>19111354</v>
-      </c>
-      <c r="E6" s="1">
-        <v>0.36399999999999999</v>
-      </c>
-      <c r="F6" s="1">
-        <v>0.81299999999999994</v>
+        <v>1255784</v>
+      </c>
+      <c r="E6" s="6">
+        <v>34</v>
+      </c>
+      <c r="F6" s="6">
+        <v>605</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>2</v>
@@ -698,27 +699,27 @@
         <v>3</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D7" s="1">
-        <v>19111357</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0.34200000000000003</v>
-      </c>
-      <c r="F7" s="3">
-        <v>0.85824999999999996</v>
+        <v>1255792</v>
+      </c>
+      <c r="E7" s="6">
+        <v>30</v>
+      </c>
+      <c r="F7" s="6">
+        <v>435</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>2</v>
@@ -727,27 +728,27 @@
         <v>3</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D8" s="1">
-        <v>19111363</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0.36199999999999999</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0.88</v>
+        <v>1255814</v>
+      </c>
+      <c r="E8" s="6">
+        <v>52</v>
+      </c>
+      <c r="F8" s="6">
+        <v>435</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>2</v>
@@ -756,27 +757,27 @@
         <v>3</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D9" s="1">
-        <v>19111369</v>
-      </c>
-      <c r="E9" s="1">
-        <v>0.34</v>
-      </c>
-      <c r="F9" s="3">
-        <v>0.68500000000000005</v>
+        <v>1255815</v>
+      </c>
+      <c r="E9" s="6">
+        <v>49.4</v>
+      </c>
+      <c r="F9" s="6">
+        <v>1500</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>2</v>
@@ -785,28 +786,26 @@
         <v>3</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B10" s="1">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D10" s="1">
-        <v>19111372</v>
-      </c>
-      <c r="E10" s="1">
-        <v>0.371</v>
-      </c>
-      <c r="F10" s="1">
-        <v>0.9</v>
-      </c>
+        <v>1212925</v>
+      </c>
+      <c r="E10" s="6">
+        <v>36</v>
+      </c>
+      <c r="F10" s="6"/>
       <c r="G10" s="1" t="s">
         <v>2</v>
       </c>
@@ -814,10 +813,10 @@
         <v>3</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
@@ -828,13 +827,13 @@
         <v>8</v>
       </c>
       <c r="D11" s="1">
-        <v>1273484</v>
-      </c>
-      <c r="E11" s="1">
-        <v>0.318</v>
-      </c>
-      <c r="F11" s="1">
-        <v>0.46500000000000002</v>
+        <v>1255785</v>
+      </c>
+      <c r="E11" s="6">
+        <v>36.4</v>
+      </c>
+      <c r="F11" s="6">
+        <v>966</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>2</v>
@@ -843,10 +842,10 @@
         <v>3</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
@@ -857,14 +856,10 @@
         <v>8</v>
       </c>
       <c r="D12" s="1">
-        <v>1273489</v>
-      </c>
-      <c r="E12" s="1">
-        <v>0.34300000000000003</v>
-      </c>
-      <c r="F12" s="1">
-        <v>0.83</v>
-      </c>
+        <v>1255791</v>
+      </c>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
       <c r="G12" s="1" t="s">
         <v>2</v>
       </c>
@@ -872,11 +867,11 @@
         <v>3</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L12" s="4"/>
-    </row>
-    <row r="13" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="K12" s="4"/>
+    </row>
+    <row r="13" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>7</v>
       </c>
@@ -884,15 +879,17 @@
         <v>69</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D13" s="1">
-        <v>1212923</v>
-      </c>
-      <c r="E13" s="1">
-        <v>0.29699999999999999</v>
-      </c>
-      <c r="F13" s="1"/>
+        <v>1255800</v>
+      </c>
+      <c r="E13" s="6">
+        <v>37</v>
+      </c>
+      <c r="F13" s="6">
+        <v>1050</v>
+      </c>
       <c r="G13" s="1" t="s">
         <v>2</v>
       </c>
@@ -900,10 +897,11 @@
         <v>3</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="K13" s="4"/>
+    </row>
+    <row r="14" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>7</v>
       </c>
@@ -911,15 +909,17 @@
         <v>69</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D14" s="1">
-        <v>1212924</v>
-      </c>
-      <c r="E14" s="1">
-        <v>0.28499999999999998</v>
-      </c>
-      <c r="F14" s="1"/>
+        <v>1255801</v>
+      </c>
+      <c r="E14" s="6">
+        <v>36.4</v>
+      </c>
+      <c r="F14" s="6">
+        <v>840</v>
+      </c>
       <c r="G14" s="1" t="s">
         <v>2</v>
       </c>
@@ -927,10 +927,11 @@
         <v>3</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="K14" s="4"/>
+    </row>
+    <row r="15" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>7</v>
       </c>
@@ -938,15 +939,17 @@
         <v>69</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D15" s="1">
-        <v>1212925</v>
-      </c>
-      <c r="E15" s="1">
-        <v>0.36</v>
-      </c>
-      <c r="F15" s="1"/>
+        <v>1255802</v>
+      </c>
+      <c r="E15" s="6">
+        <v>40.5</v>
+      </c>
+      <c r="F15" s="6">
+        <v>1180</v>
+      </c>
       <c r="G15" s="1" t="s">
         <v>2</v>
       </c>
@@ -954,27 +957,28 @@
         <v>3</v>
       </c>
       <c r="I15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K15" s="4"/>
+    </row>
+    <row r="16" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="1">
+        <v>69</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="1">
-        <v>69</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="D16" s="1">
-        <v>1255784</v>
-      </c>
-      <c r="E16" s="1">
-        <v>0.34</v>
-      </c>
-      <c r="F16" s="1">
-        <v>0.60499999999999998</v>
+        <v>1255803</v>
+      </c>
+      <c r="E16" s="6">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="F16" s="6">
+        <v>1150</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>2</v>
@@ -983,10 +987,11 @@
         <v>3</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="K16" s="4"/>
+    </row>
+    <row r="17" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>7</v>
       </c>
@@ -994,13 +999,17 @@
         <v>69</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D17" s="1">
-        <v>1255791</v>
-      </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
+        <v>1255804</v>
+      </c>
+      <c r="E17" s="6">
+        <v>38.800000000000004</v>
+      </c>
+      <c r="F17" s="6">
+        <v>1085</v>
+      </c>
       <c r="G17" s="1" t="s">
         <v>2</v>
       </c>
@@ -1010,8 +1019,9 @@
       <c r="I17" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K17" s="4"/>
+    </row>
+    <row r="18" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>7</v>
       </c>
@@ -1019,16 +1029,16 @@
         <v>69</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D18" s="1">
-        <v>1255792</v>
-      </c>
-      <c r="E18" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="F18" s="1">
-        <v>0.435</v>
+        <v>1255806</v>
+      </c>
+      <c r="E18" s="6">
+        <v>38.6</v>
+      </c>
+      <c r="F18" s="6">
+        <v>1104</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>2</v>
@@ -1037,10 +1047,11 @@
         <v>3</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="K18" s="4"/>
+    </row>
+    <row r="19" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>7</v>
       </c>
@@ -1048,388 +1059,403 @@
         <v>69</v>
       </c>
       <c r="C19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1255807</v>
+      </c>
+      <c r="E19" s="6">
+        <v>38.4</v>
+      </c>
+      <c r="F19" s="6">
+        <v>1050</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K19" s="4"/>
+    </row>
+    <row r="20" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="1">
+        <v>69</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1255810</v>
+      </c>
+      <c r="E20" s="6">
+        <v>37.9</v>
+      </c>
+      <c r="F20" s="6">
+        <v>940</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K20" s="4"/>
+    </row>
+    <row r="21" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="1">
+        <v>69</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1255811</v>
+      </c>
+      <c r="E21" s="6">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="F21" s="6">
+        <v>854</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K21" s="4"/>
+    </row>
+    <row r="22" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="1">
+        <v>69</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1255812</v>
+      </c>
+      <c r="E22" s="6">
+        <v>39.5</v>
+      </c>
+      <c r="F22" s="6">
+        <v>870</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K22" s="4"/>
+    </row>
+    <row r="23" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="1">
+        <v>73</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D23" s="1">
+        <v>19111339</v>
+      </c>
+      <c r="E23" s="6">
+        <v>35.5</v>
+      </c>
+      <c r="F23" s="6">
+        <v>903</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K23" s="4"/>
+    </row>
+    <row r="24" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="1">
+        <v>73</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D24" s="1">
+        <v>19111342</v>
+      </c>
+      <c r="E24" s="6">
+        <v>36.5</v>
+      </c>
+      <c r="F24" s="6">
+        <v>818</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K24" s="4"/>
+    </row>
+    <row r="25" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="1">
+        <v>73</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D25" s="1">
+        <v>19111348</v>
+      </c>
+      <c r="E25" s="6">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="F25" s="6">
+        <v>860</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K25" s="4"/>
+    </row>
+    <row r="26" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="1">
+        <v>73</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D26" s="1">
+        <v>19111351</v>
+      </c>
+      <c r="E26" s="6">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="F26" s="6">
+        <v>850</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K26" s="4"/>
+    </row>
+    <row r="27" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" s="1">
+        <v>73</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" s="1">
+        <v>19111354</v>
+      </c>
+      <c r="E27" s="6">
+        <v>36.4</v>
+      </c>
+      <c r="F27" s="6">
+        <v>813</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K27" s="4"/>
+    </row>
+    <row r="28" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="1">
+        <v>75</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D28" s="1">
+        <v>19111357</v>
+      </c>
+      <c r="E28" s="6">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="F28" s="6">
+        <v>858.25</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K28" s="4"/>
+    </row>
+    <row r="29" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="1">
+        <v>75</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D29" s="1">
+        <v>19111363</v>
+      </c>
+      <c r="E29" s="6">
+        <v>36.199999999999996</v>
+      </c>
+      <c r="F29" s="6">
+        <v>880</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K29" s="4"/>
+    </row>
+    <row r="30" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="1">
+        <v>75</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D30" s="1">
+        <v>19111369</v>
+      </c>
+      <c r="E30" s="6">
+        <v>34</v>
+      </c>
+      <c r="F30" s="6">
+        <v>685</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K30" s="4"/>
+    </row>
+    <row r="31" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="1">
+        <v>75</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" s="1">
+        <v>19111372</v>
+      </c>
+      <c r="E31" s="6">
+        <v>37.1</v>
+      </c>
+      <c r="F31" s="6">
+        <v>900</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K31" s="4"/>
+    </row>
+    <row r="32" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" s="1">
+        <v>69</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="1">
-        <v>1255800</v>
-      </c>
-      <c r="E19" s="1">
-        <v>0.37</v>
-      </c>
-      <c r="F19" s="1">
-        <v>1.05</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="1">
-        <v>69</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="1">
-        <v>1255801</v>
-      </c>
-      <c r="E20" s="1">
-        <v>0.36399999999999999</v>
-      </c>
-      <c r="F20" s="1">
-        <v>0.84</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" s="1">
-        <v>69</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" s="1">
-        <v>1255802</v>
-      </c>
-      <c r="E21" s="1">
-        <v>0.40500000000000003</v>
-      </c>
-      <c r="F21" s="1">
-        <v>1.18</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="1">
-        <v>69</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" s="1">
-        <v>1255803</v>
-      </c>
-      <c r="E22" s="1">
-        <v>0.372</v>
-      </c>
-      <c r="F22" s="1">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B23" s="1">
-        <v>69</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" s="1">
-        <v>1255804</v>
-      </c>
-      <c r="E23" s="1">
-        <v>0.38800000000000001</v>
-      </c>
-      <c r="F23" s="1">
-        <v>1.085</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24" s="1">
-        <v>69</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24" s="1">
-        <v>1255806</v>
-      </c>
-      <c r="E24" s="1">
-        <v>0.38600000000000001</v>
-      </c>
-      <c r="F24" s="1">
-        <v>1.1040000000000001</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" s="1">
-        <v>69</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25" s="1">
-        <v>1255807</v>
-      </c>
-      <c r="E25" s="1">
-        <v>0.38400000000000001</v>
-      </c>
-      <c r="F25" s="1">
-        <v>1.05</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B26" s="1">
-        <v>69</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D26" s="1">
-        <v>1255810</v>
-      </c>
-      <c r="E26" s="1">
-        <v>0.379</v>
-      </c>
-      <c r="F26" s="1">
-        <v>0.94</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B27" s="1">
-        <v>69</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D27" s="1">
-        <v>1255811</v>
-      </c>
-      <c r="E27" s="1">
-        <v>0.36799999999999999</v>
-      </c>
-      <c r="F27" s="1">
-        <v>0.85399999999999998</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B28" s="1">
-        <v>69</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D28" s="1">
-        <v>1255812</v>
-      </c>
-      <c r="E28" s="1">
-        <v>0.39500000000000002</v>
-      </c>
-      <c r="F28" s="1">
-        <v>0.87</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B29" s="1">
-        <v>69</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" s="1">
-        <v>1255814</v>
-      </c>
-      <c r="E29" s="1">
-        <v>0.52</v>
-      </c>
-      <c r="F29" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B30" s="1">
-        <v>69</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" s="1">
-        <v>1255815</v>
-      </c>
-      <c r="E30" s="1">
-        <v>0.49399999999999999</v>
-      </c>
-      <c r="F30" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B31" s="1">
-        <v>69</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D31" s="1">
+      <c r="D32" s="1">
         <v>1168792</v>
       </c>
-      <c r="E31" s="1">
-        <v>0.30299999999999999</v>
-      </c>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B32" s="1">
-        <v>69</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D32" s="1">
-        <v>1168793</v>
-      </c>
-      <c r="E32" s="1">
-        <v>0.34499999999999997</v>
+      <c r="E32" s="6">
+        <v>30.3</v>
       </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1" t="s">
@@ -1439,10 +1465,42 @@
         <v>3</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="K32" s="4"/>
+    </row>
+    <row r="33" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="1">
+        <v>69</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="1">
+        <v>1168793</v>
+      </c>
+      <c r="E33" s="6">
+        <v>34.5</v>
+      </c>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I33">
+    <sortCondition ref="I2:I33"/>
+    <sortCondition ref="D2:D33"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
